--- a/REDCap/TEST_CLASSIC/TEST_CLASSIC_dataset_details.xlsx
+++ b/REDCap/TEST_CLASSIC/TEST_CLASSIC_dataset_details.xlsx
@@ -140,7 +140,7 @@
     <t xml:space="preserve">last_save_time</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-06 08:05:00.748631</t>
+    <t xml:space="preserve">2026-05-10 15:18:58.385671</t>
   </si>
   <si>
     <t xml:space="preserve">final_form_tab_names</t>
